--- a/public/Nutzerstudie/Assets/Results/Analysis_Output/Identifikation/01_Identifikation_Auswertung.xlsx
+++ b/public/Nutzerstudie/Assets/Results/Analysis_Output/Identifikation/01_Identifikation_Auswertung.xlsx
@@ -90,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -108,6 +108,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -478,10 +481,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -826,36 +829,60 @@
     <row r="31" ht="50" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>IQR auffällig</t>
+          <t>Likert_Response</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Ein Einzelwert ist auffällig, wenn sein absoluter Fehler &gt; Q3 + 1,5 × (Q3 − Q1) innerhalb derselben Aufgabe/Methode liegt. Nur für n ≥ 4 und IQR &gt; 0; kein Ausschluss und kein Beweis für einen Messfehler.</t>
+          <t>Sicherheitsbewertung (1–7) aus der separaten Likert_Response-Zeile derselben Person und Aufgabe/Methode. Fehlende Werte bleiben leer; die statistische Fehleranalyse wird dadurch nicht gefiltert.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="35" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>Likert in persönlichen Rängen</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Neben jedem Methodenrang steht die Sicherheitsbewertung der Einzelaufgabe; im Gesamtvergleich der Mittelwert der bis zu vier Likert-Antworten je Person und Methode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="50" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>IQR auffällig</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Ein Einzelwert ist auffällig, wenn sein absoluter Fehler &gt; Q3 + 1,5 × (Q3 − Q1) innerhalb derselben Aufgabe/Methode liegt. Nur für n ≥ 4 und IQR &gt; 0; kein Ausschluss und kein Beweis für einen Messfehler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="35" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>Erstplatz_gewichtet</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Summe anteiliger Erstplätze: alleiniger erster Platz = 1; zwei gleich gute erste Plätze = je 0,5; drei = je 1/3. Anteil_Erstplatz_% = 100 × Summe / n.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="35" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35" ht="50" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Boxplots</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Box, Median, Mittelwert (Raute) und sämtliche beobachteten Einzelwerte; keine Daten ausgeschlossen.</t>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Standard-Boxplot: Box Q1 bis Q3 (50 %), Medianlinie, Whisker bis zum äußersten Wert innerhalb von Q1−1,5×IQR bzw. Q3+1,5×IQR; nur Werte außerhalb als Punkte. Kein Mittelwert. Alle gültigen Werte fließen in die Berechnung ein.</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1264,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C25" s="6" t="n">
@@ -1265,7 +1292,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C26" s="6" t="n">
@@ -1293,7 +1320,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C27" s="6" t="n">
@@ -1487,7 +1514,7 @@
           <t>Friedman</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D33" s="6" t="n">
@@ -1538,7 +1565,7 @@
           <t>ANOVA (Messwiederholung)</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D34" s="6" t="n">
@@ -1654,11 +1681,11 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
@@ -1747,15 +1774,20 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>Likert_Response</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>Gültig</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Zeit_s</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>IQR_auffällig</t>
         </is>
@@ -1795,13 +1827,16 @@
       <c r="I6" s="6" t="n">
         <v>99.80351839383717</v>
       </c>
-      <c r="J6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="6" t="n">
+      <c r="J6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6" t="n">
         <v>16.843</v>
       </c>
-      <c r="L6" s="4" t="b">
+      <c r="M6" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1839,13 +1874,16 @@
       <c r="I7" s="6" t="n">
         <v>30.88375849416899</v>
       </c>
-      <c r="J7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="6" t="n">
+      <c r="J7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6" t="n">
         <v>81.64100000000001</v>
       </c>
-      <c r="L7" s="4" t="b">
+      <c r="M7" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1883,13 +1921,16 @@
       <c r="I8" s="6" t="n">
         <v>31.30507552403889</v>
       </c>
-      <c r="J8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="6" t="n">
+      <c r="J8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6" t="n">
         <v>39.851</v>
       </c>
-      <c r="L8" s="4" t="b">
+      <c r="M8" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1927,13 +1968,16 @@
       <c r="I9" s="6" t="n">
         <v>27.98108584543508</v>
       </c>
-      <c r="J9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="6" t="n">
+      <c r="J9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="6" t="n">
         <v>14.307</v>
       </c>
-      <c r="L9" s="4" t="b">
+      <c r="M9" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1971,13 +2015,16 @@
       <c r="I10" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="J10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="6" t="n">
+      <c r="J10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6" t="n">
         <v>11.263</v>
       </c>
-      <c r="L10" s="4" t="b">
+      <c r="M10" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2015,13 +2062,16 @@
       <c r="I11" s="6" t="n">
         <v>31.68233213137201</v>
       </c>
-      <c r="J11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="6" t="n">
+      <c r="J11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6" t="n">
         <v>19.968</v>
       </c>
-      <c r="L11" s="4" t="b">
+      <c r="M11" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2059,13 +2109,16 @@
       <c r="I12" s="6" t="n">
         <v>43.77674525882834</v>
       </c>
-      <c r="J12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
+      <c r="J12" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6" t="n">
         <v>186.569</v>
       </c>
-      <c r="L12" s="4" t="b">
+      <c r="M12" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2103,13 +2156,16 @@
       <c r="I13" s="6" t="n">
         <v>42.31382876620111</v>
       </c>
-      <c r="J13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="6" t="n">
+      <c r="J13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="6" t="n">
         <v>60.724</v>
       </c>
-      <c r="L13" s="4" t="b">
+      <c r="M13" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2147,13 +2203,16 @@
       <c r="I14" s="6" t="n">
         <v>38.15309738109182</v>
       </c>
-      <c r="J14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="6" t="n">
+      <c r="J14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="6" t="n">
         <v>57.771</v>
       </c>
-      <c r="L14" s="4" t="b">
+      <c r="M14" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2185,13 +2244,16 @@
       </c>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6" t="n">
+      <c r="J15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6" t="n">
         <v>63.311</v>
       </c>
-      <c r="L15" s="4" t="b">
+      <c r="M15" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2229,13 +2291,16 @@
       <c r="I16" s="6" t="n">
         <v>61.5843292632772</v>
       </c>
-      <c r="J16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" s="6" t="n">
+      <c r="J16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="6" t="n">
         <v>28.222</v>
       </c>
-      <c r="L16" s="4" t="b">
+      <c r="M16" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2273,13 +2338,16 @@
       <c r="I17" s="6" t="n">
         <v>99.34022528907562</v>
       </c>
-      <c r="J17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" s="6" t="n">
+      <c r="J17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="6" t="n">
         <v>124.907</v>
       </c>
-      <c r="L17" s="4" t="b">
+      <c r="M17" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2317,13 +2385,16 @@
       <c r="I18" s="6" t="n">
         <v>47.02889312996408</v>
       </c>
-      <c r="J18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="6" t="n">
+      <c r="J18" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6" t="n">
         <v>77.044</v>
       </c>
-      <c r="L18" s="4" t="b">
+      <c r="M18" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2361,13 +2432,16 @@
       <c r="I19" s="6" t="n">
         <v>61.00786621463389</v>
       </c>
-      <c r="J19" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="6" t="n">
+      <c r="J19" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6" t="n">
         <v>45.788</v>
       </c>
-      <c r="L19" s="4" t="b">
+      <c r="M19" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2405,13 +2479,16 @@
       <c r="I20" s="6" t="n">
         <v>41.55797675598935</v>
       </c>
-      <c r="J20" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" s="6" t="n">
+      <c r="J20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6" t="n">
         <v>115.971</v>
       </c>
-      <c r="L20" s="4" t="b">
+      <c r="M20" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2449,13 +2526,16 @@
       <c r="I21" s="6" t="n">
         <v>25.25940816197958</v>
       </c>
-      <c r="J21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="6" t="n">
+      <c r="J21" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="6" t="n">
         <v>83.563</v>
       </c>
-      <c r="L21" s="4" t="b">
+      <c r="M21" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2493,13 +2573,16 @@
       <c r="I22" s="6" t="n">
         <v>5.018128007253322</v>
       </c>
-      <c r="J22" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="6" t="n">
+      <c r="J22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="6" t="n">
         <v>113.19</v>
       </c>
-      <c r="L22" s="4" t="b">
+      <c r="M22" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2537,13 +2620,16 @@
       <c r="I23" s="6" t="n">
         <v>99.9960434933357</v>
       </c>
-      <c r="J23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="6" t="n">
+      <c r="J23" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="6" t="n">
         <v>38.968</v>
       </c>
-      <c r="L23" s="4" t="b">
+      <c r="M23" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2581,13 +2667,16 @@
       <c r="I24" s="6" t="n">
         <v>17.09910497159589</v>
       </c>
-      <c r="J24" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="6" t="n">
+      <c r="J24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="6" t="n">
         <v>146.178</v>
       </c>
-      <c r="L24" s="4" t="b">
+      <c r="M24" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2625,13 +2714,16 @@
       <c r="I25" s="6" t="n">
         <v>4.612880656014729</v>
       </c>
-      <c r="J25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="6" t="n">
+      <c r="J25" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6" t="n">
         <v>78.086</v>
       </c>
-      <c r="L25" s="4" t="b">
+      <c r="M25" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2669,13 +2761,16 @@
       <c r="I26" s="6" t="n">
         <v>5.018128007253322</v>
       </c>
-      <c r="J26" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="6" t="n">
+      <c r="J26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="6" t="n">
         <v>49.55</v>
       </c>
-      <c r="L26" s="4" t="b">
+      <c r="M26" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2713,13 +2808,16 @@
       <c r="I27" s="6" t="n">
         <v>39.56135878519856</v>
       </c>
-      <c r="J27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" s="6" t="n">
+      <c r="J27" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="6" t="n">
         <v>31.649</v>
       </c>
-      <c r="L27" s="4" t="b">
+      <c r="M27" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2757,13 +2855,16 @@
       <c r="I28" s="6" t="n">
         <v>41.55797675598935</v>
       </c>
-      <c r="J28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" s="6" t="n">
+      <c r="J28" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="6" t="n">
         <v>12.446</v>
       </c>
-      <c r="L28" s="4" t="b">
+      <c r="M28" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2801,13 +2902,16 @@
       <c r="I29" s="6" t="n">
         <v>41.02216929182877</v>
       </c>
-      <c r="J29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" s="6" t="n">
+      <c r="J29" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="6" t="n">
         <v>17.854</v>
       </c>
-      <c r="L29" s="4" t="b">
+      <c r="M29" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2845,13 +2949,16 @@
       <c r="I30" s="6" t="n">
         <v>44.89455276555509</v>
       </c>
-      <c r="J30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" s="6" t="n">
+      <c r="J30" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="6" t="n">
         <v>33.257</v>
       </c>
-      <c r="L30" s="4" t="b">
+      <c r="M30" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2889,13 +2996,16 @@
       <c r="I31" s="6" t="n">
         <v>32.21321139546893</v>
       </c>
-      <c r="J31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" s="6" t="n">
+      <c r="J31" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6" t="n">
         <v>20.868</v>
       </c>
-      <c r="L31" s="4" t="b">
+      <c r="M31" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2933,13 +3043,16 @@
       <c r="I32" s="6" t="n">
         <v>38.15309738109182</v>
       </c>
-      <c r="J32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" s="6" t="n">
+      <c r="J32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" s="6" t="n">
         <v>40.154</v>
       </c>
-      <c r="L32" s="4" t="b">
+      <c r="M32" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2977,13 +3090,16 @@
       <c r="I33" s="6" t="n">
         <v>19.62168778003666</v>
       </c>
-      <c r="J33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" s="6" t="n">
+      <c r="J33" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" s="6" t="n">
         <v>256.433</v>
       </c>
-      <c r="L33" s="4" t="b">
+      <c r="M33" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3021,13 +3137,16 @@
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" s="6" t="n">
+      <c r="J34" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="6" t="n">
         <v>134.484</v>
       </c>
-      <c r="L34" s="4" t="b">
+      <c r="M34" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3065,13 +3184,16 @@
       <c r="I35" s="6" t="n">
         <v>27.98108584543508</v>
       </c>
-      <c r="J35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" s="6" t="n">
+      <c r="J35" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="6" t="n">
         <v>40.705</v>
       </c>
-      <c r="L35" s="4" t="b">
+      <c r="M35" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3109,13 +3231,16 @@
       <c r="I36" s="6" t="n">
         <v>39.56135878519856</v>
       </c>
-      <c r="J36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" s="6" t="n">
+      <c r="J36" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="6" t="n">
         <v>18.352</v>
       </c>
-      <c r="L36" s="4" t="b">
+      <c r="M36" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3153,13 +3278,16 @@
       <c r="I37" s="6" t="n">
         <v>38.97507927991641</v>
       </c>
-      <c r="J37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K37" s="6" t="n">
+      <c r="J37" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="6" t="n">
         <v>15.43</v>
       </c>
-      <c r="L37" s="4" t="b">
+      <c r="M37" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3197,13 +3325,16 @@
       <c r="I38" s="6" t="n">
         <v>61.00786621463389</v>
       </c>
-      <c r="J38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K38" s="6" t="n">
+      <c r="J38" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="6" t="n">
         <v>17.374</v>
       </c>
-      <c r="L38" s="4" t="b">
+      <c r="M38" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3241,13 +3372,16 @@
       <c r="I39" s="6" t="n">
         <v>6.49631944082691</v>
       </c>
-      <c r="J39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" s="6" t="n">
+      <c r="J39" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="6" t="n">
         <v>27.288</v>
       </c>
-      <c r="L39" s="4" t="b">
+      <c r="M39" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3285,13 +3419,16 @@
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K40" s="6" t="n">
+      <c r="J40" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="6" t="n">
         <v>38.386</v>
       </c>
-      <c r="L40" s="4" t="b">
+      <c r="M40" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3329,13 +3466,16 @@
       <c r="I41" s="6" t="n">
         <v>50.81302353189629</v>
       </c>
-      <c r="J41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K41" s="6" t="n">
+      <c r="J41" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" s="6" t="n">
         <v>37.647</v>
       </c>
-      <c r="L41" s="4" t="b">
+      <c r="M41" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3373,13 +3513,16 @@
       <c r="I42" s="6" t="n">
         <v>2.849560205286445</v>
       </c>
-      <c r="J42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K42" s="6" t="n">
+      <c r="J42" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" s="6" t="n">
         <v>21.881</v>
       </c>
-      <c r="L42" s="4" t="b">
+      <c r="M42" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3417,13 +3560,16 @@
       <c r="I43" s="6" t="n">
         <v>30.88375849416899</v>
       </c>
-      <c r="J43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K43" s="6" t="n">
+      <c r="J43" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" s="6" t="n">
         <v>50.507</v>
       </c>
-      <c r="L43" s="4" t="b">
+      <c r="M43" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3461,13 +3607,16 @@
       <c r="I44" s="6" t="n">
         <v>4.612880656014729</v>
       </c>
-      <c r="J44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K44" s="6" t="n">
+      <c r="J44" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="6" t="n">
         <v>29.567</v>
       </c>
-      <c r="L44" s="4" t="b">
+      <c r="M44" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3505,13 +3654,16 @@
       <c r="I45" s="6" t="n">
         <v>2.849560205286445</v>
       </c>
-      <c r="J45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K45" s="6" t="n">
+      <c r="J45" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" s="6" t="n">
         <v>81.55</v>
       </c>
-      <c r="L45" s="4" t="b">
+      <c r="M45" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3549,13 +3701,16 @@
       <c r="I46" s="6" t="n">
         <v>4.612880656014729</v>
       </c>
-      <c r="J46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K46" s="6" t="n">
+      <c r="J46" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" s="6" t="n">
         <v>27.166</v>
       </c>
-      <c r="L46" s="4" t="b">
+      <c r="M46" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3593,13 +3748,16 @@
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K47" s="6" t="n">
+      <c r="J47" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" s="6" t="n">
         <v>25.653</v>
       </c>
-      <c r="L47" s="4" t="b">
+      <c r="M47" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3637,13 +3795,16 @@
       <c r="I48" s="6" t="n">
         <v>28.03910307379777</v>
       </c>
-      <c r="J48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K48" s="6" t="n">
+      <c r="J48" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" s="6" t="n">
         <v>41.596</v>
       </c>
-      <c r="L48" s="4" t="b">
+      <c r="M48" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3681,13 +3842,16 @@
       <c r="I49" s="6" t="n">
         <v>30.88375849416899</v>
       </c>
-      <c r="J49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K49" s="6" t="n">
+      <c r="J49" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" s="6" t="n">
         <v>21.526</v>
       </c>
-      <c r="L49" s="4" t="b">
+      <c r="M49" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3725,13 +3889,16 @@
       <c r="I50" s="6" t="n">
         <v>41.55797675598935</v>
       </c>
-      <c r="J50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K50" s="6" t="n">
+      <c r="J50" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" s="6" t="n">
         <v>16.087</v>
       </c>
-      <c r="L50" s="4" t="b">
+      <c r="M50" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3745,7 +3912,7 @@
     <row r="54" ht="29" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Mittel = Summe / n; Median = mittlerer sortierter Wert; SD = Stichprobenstandardabweichung (ddof=1); Q1/Q3 = 25./75. Perzentil.</t>
+          <t>Mittel = Summe / n; Median = mittlerer sortierter Wert; SD = Stichprobenstandardabweichung (ddof=1); Q1/Q3 = 25./75. Perzentil; IQR = Q3 − Q1.</t>
         </is>
       </c>
     </row>
@@ -3817,10 +3984,15 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
+          <t>Fehler % IQR</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
           <t>Zeit s Mittel</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>Zeit s Median</t>
         </is>
@@ -3832,16 +4004,16 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B56" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="7" t="n">
+      <c r="C56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
@@ -3869,9 +4041,12 @@
         <v>46.18550014394282</v>
       </c>
       <c r="N56" s="6" t="n">
+        <v>16.54241945920583</v>
+      </c>
+      <c r="O56" s="6" t="n">
         <v>44.80180000000001</v>
       </c>
-      <c r="O56" s="6" t="n">
+      <c r="P56" s="6" t="n">
         <v>38.968</v>
       </c>
     </row>
@@ -3881,16 +4056,16 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="7" t="n">
+      <c r="C57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="7" t="n">
+      <c r="E57" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
@@ -3918,9 +4093,12 @@
         <v>41.93590276109523</v>
       </c>
       <c r="N57" s="6" t="n">
+        <v>37.1203984294612</v>
+      </c>
+      <c r="O57" s="6" t="n">
         <v>49.31513333333332</v>
       </c>
-      <c r="O57" s="6" t="n">
+      <c r="P57" s="6" t="n">
         <v>38.386</v>
       </c>
     </row>
@@ -3930,16 +4108,16 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B58" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="C58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="7" t="n">
+      <c r="C58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="6" t="n">
@@ -3967,9 +4145,12 @@
         <v>42.72289864042089</v>
       </c>
       <c r="N58" s="6" t="n">
+        <v>24.99314796671481</v>
+      </c>
+      <c r="O58" s="6" t="n">
         <v>74.03642857142856</v>
       </c>
-      <c r="O58" s="6" t="n">
+      <c r="P58" s="6" t="n">
         <v>37.4265</v>
       </c>
     </row>
@@ -3983,7 +4164,7 @@
     <row r="62" ht="29" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Nur vollständige Methodentripel; kleinster Fehler erhält Rang 1; Gleichstände erhalten Mittelränge.</t>
+          <t>Nur vollständige Methodentripel; kleinster Fehler erhält Rang 1; Gleichstände erhalten Mittelränge. Neben dem Rang steht die Likert-Sicherheit (1–7) je Methode.</t>
         </is>
       </c>
     </row>
@@ -4000,12 +4181,27 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
+          <t>Likert_VSUP</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Likert_Scaled Glyph</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Likert_IsoGlyph</t>
         </is>
       </c>
     </row>
@@ -4018,10 +4214,19 @@
       <c r="B64" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C64" s="6" t="n">
-        <v>1</v>
+      <c r="C64" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="D64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" s="7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4034,11 +4239,20 @@
       <c r="B65" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C65" s="6" t="n">
+      <c r="C65" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D65" s="6" t="n">
-        <v>1</v>
+      <c r="E65" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -4050,11 +4264,20 @@
       <c r="B66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C66" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="E66" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -4066,11 +4289,20 @@
       <c r="B67" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C67" s="6" t="n">
+      <c r="C67" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="E67" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -4082,11 +4314,20 @@
       <c r="B68" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="6" t="n">
-        <v>1</v>
+      <c r="C68" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="D68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -4098,10 +4339,19 @@
       <c r="B69" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C69" s="6" t="n">
-        <v>1</v>
+      <c r="C69" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="D69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" s="7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4114,11 +4364,20 @@
       <c r="B70" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C70" s="6" t="n">
+      <c r="C70" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D70" s="6" t="n">
-        <v>1</v>
+      <c r="E70" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -4130,11 +4389,20 @@
       <c r="B71" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="6" t="n">
-        <v>1</v>
+      <c r="C71" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="D71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -4146,11 +4414,20 @@
       <c r="B72" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="6" t="n">
-        <v>1</v>
+      <c r="C72" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="D72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -4162,11 +4439,20 @@
       <c r="B73" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C73" s="6" t="n">
-        <v>1</v>
+      <c r="C73" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="D73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -4178,11 +4464,20 @@
       <c r="B74" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C74" s="6" t="n">
-        <v>1</v>
+      <c r="C74" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="D74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -4194,11 +4489,20 @@
       <c r="B75" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C75" s="6" t="n">
+      <c r="C75" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D75" s="6" t="n">
-        <v>1</v>
+      <c r="E75" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -4210,11 +4514,20 @@
       <c r="B76" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C76" s="6" t="n">
+      <c r="C76" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D76" s="6" t="n">
+      <c r="E76" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -4226,11 +4539,20 @@
       <c r="B77" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C77" s="6" t="n">
+      <c r="C77" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D77" s="6" t="n">
-        <v>1</v>
+      <c r="E77" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="80" ht="29" customHeight="1">
@@ -4300,7 +4622,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B83" s="7" t="n">
+      <c r="B83" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C83" s="6" t="n">
@@ -4312,16 +4634,16 @@
       <c r="E83" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F83" s="7" t="n">
+      <c r="F83" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H83" s="7" t="n">
+      <c r="H83" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I83" s="7" t="n">
+      <c r="I83" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4331,7 +4653,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B84" s="7" t="n">
+      <c r="B84" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C84" s="6" t="n">
@@ -4343,16 +4665,16 @@
       <c r="E84" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="F84" s="7" t="n">
+      <c r="F84" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="G84" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H84" s="7" t="n">
+      <c r="H84" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I84" s="7" t="n">
+      <c r="I84" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4362,7 +4684,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B85" s="7" t="n">
+      <c r="B85" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C85" s="6" t="n">
@@ -4374,16 +4696,16 @@
       <c r="E85" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F85" s="7" t="n">
+      <c r="F85" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="G85" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H85" s="7" t="n">
+      <c r="H85" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I85" s="7" t="n">
+      <c r="I85" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4569,7 +4891,7 @@
           <t>Friedman</t>
         </is>
       </c>
-      <c r="C91" s="7" t="n">
+      <c r="C91" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D91" s="6" t="n">
@@ -4617,7 +4939,7 @@
       <c r="AD91" s="4" t="n"/>
       <c r="AE91" s="4" t="n"/>
     </row>
-    <row r="92" ht="35" customHeight="1">
+    <row r="92" ht="80" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Niederschlag_Uncertainty_Maxima</t>
@@ -4628,7 +4950,7 @@
           <t>ANOVA (Messwiederholung)</t>
         </is>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C92" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D92" s="6" t="n">
@@ -4750,13 +5072,13 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
@@ -4843,15 +5165,20 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>Likert_Response</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>Gültig</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Zeit_s</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>IQR_auffällig</t>
         </is>
@@ -4891,13 +5218,16 @@
       <c r="I6" s="6" t="n">
         <v>0.533568162776351</v>
       </c>
-      <c r="J6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="6" t="n">
+      <c r="J6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6" t="n">
         <v>75.239</v>
       </c>
-      <c r="L6" s="4" t="b">
+      <c r="M6" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4935,13 +5265,16 @@
       <c r="I7" s="6" t="n">
         <v>1.365339659687163</v>
       </c>
-      <c r="J7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="6" t="n">
+      <c r="J7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6" t="n">
         <v>39.61</v>
       </c>
-      <c r="L7" s="4" t="b">
+      <c r="M7" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4979,13 +5312,16 @@
       <c r="I8" s="6" t="n">
         <v>1.033718543057625</v>
       </c>
-      <c r="J8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="6" t="n">
+      <c r="J8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6" t="n">
         <v>11.787</v>
       </c>
-      <c r="L8" s="4" t="b">
+      <c r="M8" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5023,13 +5359,16 @@
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="6" t="n">
+      <c r="J9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="6" t="n">
         <v>15.326</v>
       </c>
-      <c r="L9" s="4" t="b">
+      <c r="M9" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5067,13 +5406,16 @@
       <c r="I10" s="6" t="n">
         <v>0.4040193638886707</v>
       </c>
-      <c r="J10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="6" t="n">
+      <c r="J10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6" t="n">
         <v>25.929</v>
       </c>
-      <c r="L10" s="4" t="b">
+      <c r="M10" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5111,13 +5453,16 @@
       <c r="I11" s="6" t="n">
         <v>30.37161136203869</v>
       </c>
-      <c r="J11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="6" t="n">
+      <c r="J11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6" t="n">
         <v>16.412</v>
       </c>
-      <c r="L11" s="4" t="b">
+      <c r="M11" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5155,13 +5500,16 @@
       <c r="I12" s="6" t="n">
         <v>0.6291348459936146</v>
       </c>
-      <c r="J12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
+      <c r="J12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6" t="n">
         <v>58.568</v>
       </c>
-      <c r="L12" s="4" t="b">
+      <c r="M12" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5199,13 +5547,16 @@
       <c r="I13" s="6" t="n">
         <v>2.316354452811438</v>
       </c>
-      <c r="J13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="6" t="n">
+      <c r="J13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="6" t="n">
         <v>52.858</v>
       </c>
-      <c r="L13" s="4" t="b">
+      <c r="M13" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5243,13 +5594,16 @@
       <c r="I14" s="6" t="n">
         <v>0.6983955190085469</v>
       </c>
-      <c r="J14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="6" t="n">
+      <c r="J14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="6" t="n">
         <v>96.77</v>
       </c>
-      <c r="L14" s="4" t="b">
+      <c r="M14" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5287,13 +5641,16 @@
       <c r="I15" s="6" t="n">
         <v>91.97258466376458</v>
       </c>
-      <c r="J15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" s="6" t="n">
+      <c r="J15" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6" t="n">
         <v>21.29</v>
       </c>
-      <c r="L15" s="4" t="b">
+      <c r="M15" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5325,13 +5682,16 @@
       </c>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="n">
+      <c r="J16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6" t="n">
         <v>58.788</v>
       </c>
-      <c r="L16" s="4" t="b">
+      <c r="M16" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5363,13 +5723,16 @@
       </c>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6" t="n">
+      <c r="J17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6" t="n">
         <v>26.154</v>
       </c>
-      <c r="L17" s="4" t="b">
+      <c r="M17" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5407,13 +5770,16 @@
       <c r="I18" s="6" t="n">
         <v>1.040861623332128</v>
       </c>
-      <c r="J18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="6" t="n">
+      <c r="J18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6" t="n">
         <v>108.86</v>
       </c>
-      <c r="L18" s="4" t="b">
+      <c r="M18" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5451,13 +5817,16 @@
       <c r="I19" s="6" t="n">
         <v>0.9541491856630114</v>
       </c>
-      <c r="J19" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="6" t="n">
+      <c r="J19" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6" t="n">
         <v>70.114</v>
       </c>
-      <c r="L19" s="4" t="b">
+      <c r="M19" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5495,13 +5864,16 @@
       <c r="I20" s="6" t="n">
         <v>49.21226069632303</v>
       </c>
-      <c r="J20" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" s="6" t="n">
+      <c r="J20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6" t="n">
         <v>105.291</v>
       </c>
-      <c r="L20" s="4" t="b">
+      <c r="M20" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5539,13 +5911,16 @@
       <c r="I21" s="6" t="n">
         <v>0.2366086969719</v>
       </c>
-      <c r="J21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="6" t="n">
+      <c r="J21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="6" t="n">
         <v>36.092</v>
       </c>
-      <c r="L21" s="4" t="b">
+      <c r="M21" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5583,13 +5958,16 @@
       <c r="I22" s="6" t="n">
         <v>3.556595776329476</v>
       </c>
-      <c r="J22" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="6" t="n">
+      <c r="J22" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="6" t="n">
         <v>53.779</v>
       </c>
-      <c r="L22" s="4" t="b">
+      <c r="M22" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5627,13 +6005,16 @@
       <c r="I23" s="6" t="n">
         <v>0.007414919955298784</v>
       </c>
-      <c r="J23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="6" t="n">
+      <c r="J23" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="6" t="n">
         <v>40.334</v>
       </c>
-      <c r="L23" s="4" t="b">
+      <c r="M23" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5671,13 +6052,16 @@
       <c r="I24" s="6" t="n">
         <v>0.0411195578526509</v>
       </c>
-      <c r="J24" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="6" t="n">
+      <c r="J24" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="6" t="n">
         <v>87.122</v>
       </c>
-      <c r="L24" s="4" t="b">
+      <c r="M24" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5715,13 +6099,16 @@
       <c r="I25" s="6" t="n">
         <v>1.31095563594379</v>
       </c>
-      <c r="J25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="6" t="n">
+      <c r="J25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6" t="n">
         <v>183.99</v>
       </c>
-      <c r="L25" s="4" t="b">
+      <c r="M25" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5759,13 +6146,16 @@
       <c r="I26" s="6" t="n">
         <v>0.02259859416251884</v>
       </c>
-      <c r="J26" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="6" t="n">
+      <c r="J26" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="6" t="n">
         <v>31.738</v>
       </c>
-      <c r="L26" s="4" t="b">
+      <c r="M26" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5803,13 +6193,16 @@
       <c r="I27" s="6" t="n">
         <v>0.5459537157273002</v>
       </c>
-      <c r="J27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" s="6" t="n">
+      <c r="J27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="6" t="n">
         <v>11.048</v>
       </c>
-      <c r="L27" s="4" t="b">
+      <c r="M27" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5847,13 +6240,16 @@
       <c r="I28" s="6" t="n">
         <v>38.99213378536611</v>
       </c>
-      <c r="J28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" s="6" t="n">
+      <c r="J28" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="6" t="n">
         <v>10.711</v>
       </c>
-      <c r="L28" s="4" t="b">
+      <c r="M28" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5891,13 +6287,16 @@
       <c r="I29" s="6" t="n">
         <v>2.181097812059075</v>
       </c>
-      <c r="J29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" s="6" t="n">
+      <c r="J29" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="6" t="n">
         <v>16.978</v>
       </c>
-      <c r="L29" s="4" t="b">
+      <c r="M29" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5935,13 +6334,16 @@
       <c r="I30" s="6" t="n">
         <v>0.5595185381948814</v>
       </c>
-      <c r="J30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" s="6" t="n">
+      <c r="J30" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="6" t="n">
         <v>19.504</v>
       </c>
-      <c r="L30" s="4" t="b">
+      <c r="M30" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5979,13 +6381,16 @@
       <c r="I31" s="6" t="n">
         <v>1.75226493275167</v>
       </c>
-      <c r="J31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" s="6" t="n">
+      <c r="J31" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6" t="n">
         <v>170.5</v>
       </c>
-      <c r="L31" s="4" t="b">
+      <c r="M31" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6023,13 +6428,16 @@
       <c r="I32" s="6" t="n">
         <v>3.549774392647167</v>
       </c>
-      <c r="J32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" s="6" t="n">
+      <c r="J32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" s="6" t="n">
         <v>15.869</v>
       </c>
-      <c r="L32" s="4" t="b">
+      <c r="M32" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6067,13 +6475,16 @@
       <c r="I33" s="6" t="n">
         <v>0.0003887133639875507</v>
       </c>
-      <c r="J33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" s="6" t="n">
+      <c r="J33" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" s="6" t="n">
         <v>126.562</v>
       </c>
-      <c r="L33" s="4" t="b">
+      <c r="M33" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6111,13 +6522,16 @@
       <c r="I34" s="6" t="n">
         <v>1.776152929443725</v>
       </c>
-      <c r="J34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" s="6" t="n">
+      <c r="J34" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="6" t="n">
         <v>113.015</v>
       </c>
-      <c r="L34" s="4" t="b">
+      <c r="M34" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6155,13 +6569,16 @@
       <c r="I35" s="6" t="n">
         <v>0.0003887133639875507</v>
       </c>
-      <c r="J35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" s="6" t="n">
+      <c r="J35" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="6" t="n">
         <v>70.26000000000001</v>
       </c>
-      <c r="L35" s="4" t="b">
+      <c r="M35" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6199,13 +6616,16 @@
       <c r="I36" s="6" t="n">
         <v>1.48976927354169</v>
       </c>
-      <c r="J36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" s="6" t="n">
+      <c r="J36" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="6" t="n">
         <v>14.032</v>
       </c>
-      <c r="L36" s="4" t="b">
+      <c r="M36" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6243,13 +6663,16 @@
       <c r="I37" s="6" t="n">
         <v>0.8083777659039347</v>
       </c>
-      <c r="J37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K37" s="6" t="n">
+      <c r="J37" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="6" t="n">
         <v>11.729</v>
       </c>
-      <c r="L37" s="4" t="b">
+      <c r="M37" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6287,13 +6710,16 @@
       <c r="I38" s="6" t="n">
         <v>1.219178171102477</v>
       </c>
-      <c r="J38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K38" s="6" t="n">
+      <c r="J38" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="6" t="n">
         <v>26.916</v>
       </c>
-      <c r="L38" s="4" t="b">
+      <c r="M38" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6331,13 +6757,16 @@
       <c r="I39" s="6" t="n">
         <v>0.020408221347917</v>
       </c>
-      <c r="J39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" s="6" t="n">
+      <c r="J39" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="6" t="n">
         <v>10.855</v>
       </c>
-      <c r="L39" s="4" t="b">
+      <c r="M39" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6375,13 +6804,16 @@
       <c r="I40" s="6" t="n">
         <v>0.007564393998705471</v>
       </c>
-      <c r="J40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K40" s="6" t="n">
+      <c r="J40" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="6" t="n">
         <v>35.774</v>
       </c>
-      <c r="L40" s="4" t="b">
+      <c r="M40" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6419,13 +6851,16 @@
       <c r="I41" s="6" t="n">
         <v>0.5810241674967406</v>
       </c>
-      <c r="J41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K41" s="6" t="n">
+      <c r="J41" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" s="6" t="n">
         <v>36.948</v>
       </c>
-      <c r="L41" s="4" t="b">
+      <c r="M41" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6463,13 +6898,16 @@
       <c r="I42" s="6" t="n">
         <v>0.5810241674967406</v>
       </c>
-      <c r="J42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K42" s="6" t="n">
+      <c r="J42" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" s="6" t="n">
         <v>44.277</v>
       </c>
-      <c r="L42" s="4" t="b">
+      <c r="M42" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6507,13 +6945,16 @@
       <c r="I43" s="6" t="n">
         <v>0.005902856443478786</v>
       </c>
-      <c r="J43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K43" s="6" t="n">
+      <c r="J43" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" s="6" t="n">
         <v>21.08</v>
       </c>
-      <c r="L43" s="4" t="b">
+      <c r="M43" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6551,13 +6992,16 @@
       <c r="I44" s="6" t="n">
         <v>0.1214329563811354</v>
       </c>
-      <c r="J44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K44" s="6" t="n">
+      <c r="J44" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="6" t="n">
         <v>11.895</v>
       </c>
-      <c r="L44" s="4" t="b">
+      <c r="M44" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6595,13 +7039,16 @@
       <c r="I45" s="6" t="n">
         <v>0.02262812341941233</v>
       </c>
-      <c r="J45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K45" s="6" t="n">
+      <c r="J45" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" s="6" t="n">
         <v>35.685</v>
       </c>
-      <c r="L45" s="4" t="b">
+      <c r="M45" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6639,13 +7086,16 @@
       <c r="I46" s="6" t="n">
         <v>0.7467223193254292</v>
       </c>
-      <c r="J46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K46" s="6" t="n">
+      <c r="J46" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" s="6" t="n">
         <v>158.032</v>
       </c>
-      <c r="L46" s="4" t="b">
+      <c r="M46" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6683,13 +7133,16 @@
       <c r="I47" s="6" t="n">
         <v>94.88420327656038</v>
       </c>
-      <c r="J47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K47" s="6" t="n">
+      <c r="J47" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" s="6" t="n">
         <v>460.744</v>
       </c>
-      <c r="L47" s="4" t="b">
+      <c r="M47" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6727,13 +7180,16 @@
       <c r="I48" s="6" t="n">
         <v>1.828030568151923</v>
       </c>
-      <c r="J48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K48" s="6" t="n">
+      <c r="J48" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" s="6" t="n">
         <v>26.358</v>
       </c>
-      <c r="L48" s="4" t="b">
+      <c r="M48" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6771,13 +7227,16 @@
       <c r="I49" s="6" t="n">
         <v>1.372383900488059</v>
       </c>
-      <c r="J49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K49" s="6" t="n">
+      <c r="J49" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="L49" s="4" t="b">
+      <c r="M49" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6815,13 +7274,16 @@
       <c r="I50" s="6" t="n">
         <v>1.365807687183427</v>
       </c>
-      <c r="J50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K50" s="6" t="n">
+      <c r="J50" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" s="6" t="n">
         <v>12.123</v>
       </c>
-      <c r="L50" s="4" t="b">
+      <c r="M50" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6835,7 +7297,7 @@
     <row r="54" ht="29" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Mittel = Summe / n; Median = mittlerer sortierter Wert; SD = Stichprobenstandardabweichung (ddof=1); Q1/Q3 = 25./75. Perzentil.</t>
+          <t>Mittel = Summe / n; Median = mittlerer sortierter Wert; SD = Stichprobenstandardabweichung (ddof=1); Q1/Q3 = 25./75. Perzentil; IQR = Q3 − Q1.</t>
         </is>
       </c>
     </row>
@@ -6907,10 +7369,15 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
+          <t>Fehler % IQR</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
           <t>Zeit s Mittel</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>Zeit s Median</t>
         </is>
@@ -6922,16 +7389,16 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B56" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="C56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="7" t="n">
+      <c r="C56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F56" s="6" t="n">
@@ -6959,9 +7426,12 @@
         <v>3.207605247500144</v>
       </c>
       <c r="N56" s="6" t="n">
+        <v>2.971274488340107</v>
+      </c>
+      <c r="O56" s="6" t="n">
         <v>68.14750000000001</v>
       </c>
-      <c r="O56" s="6" t="n">
+      <c r="P56" s="6" t="n">
         <v>29.327</v>
       </c>
     </row>
@@ -6971,16 +7441,16 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="C57" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="7" t="n">
+      <c r="C57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F57" s="6" t="n">
@@ -7008,9 +7478,12 @@
         <v>1.770180930270711</v>
       </c>
       <c r="N57" s="6" t="n">
+        <v>1.008044749300655</v>
+      </c>
+      <c r="O57" s="6" t="n">
         <v>68.80864285714287</v>
       </c>
-      <c r="O57" s="6" t="n">
+      <c r="P57" s="6" t="n">
         <v>46.23399999999999</v>
       </c>
     </row>
@@ -7020,16 +7493,16 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B58" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="7" t="n">
+      <c r="C58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="8" t="n">
         <v>11</v>
       </c>
       <c r="F58" s="6" t="n">
@@ -7057,9 +7530,12 @@
         <v>0.8349982346628714</v>
       </c>
       <c r="N58" s="6" t="n">
+        <v>0.8031243940268398</v>
+      </c>
+      <c r="O58" s="6" t="n">
         <v>46.05453333333333</v>
       </c>
-      <c r="O58" s="6" t="n">
+      <c r="P58" s="6" t="n">
         <v>35.685</v>
       </c>
     </row>
@@ -7073,7 +7549,7 @@
     <row r="62" ht="29" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Nur vollständige Methodentripel; kleinster Fehler erhält Rang 1; Gleichstände erhalten Mittelränge.</t>
+          <t>Nur vollständige Methodentripel; kleinster Fehler erhält Rang 1; Gleichstände erhalten Mittelränge. Neben dem Rang steht die Likert-Sicherheit (1–7) je Methode.</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7566,27 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
+          <t>Likert_VSUP</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Likert_Scaled Glyph</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Likert_IsoGlyph</t>
         </is>
       </c>
     </row>
@@ -7108,11 +7599,20 @@
       <c r="B64" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C64" s="6" t="n">
+      <c r="C64" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -7124,11 +7624,20 @@
       <c r="B65" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C65" s="6" t="n">
+      <c r="C65" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D65" s="6" t="n">
-        <v>1</v>
+      <c r="E65" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -7140,11 +7649,20 @@
       <c r="B66" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C66" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D66" s="6" t="n">
-        <v>1</v>
+      <c r="E66" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -7156,11 +7674,20 @@
       <c r="B67" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C67" s="6" t="n">
+      <c r="C67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -7172,11 +7699,20 @@
       <c r="B68" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C68" s="6" t="n">
+      <c r="C68" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="E68" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -7188,11 +7724,20 @@
       <c r="B69" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C69" s="6" t="n">
+      <c r="C69" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="E69" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -7204,11 +7749,20 @@
       <c r="B70" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C70" s="6" t="n">
+      <c r="C70" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D70" s="6" t="n">
-        <v>1</v>
+      <c r="E70" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -7220,11 +7774,20 @@
       <c r="B71" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C71" s="6" t="n">
+      <c r="C71" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D71" s="6" t="n">
-        <v>1</v>
+      <c r="E71" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -7236,11 +7799,20 @@
       <c r="B72" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="C72" s="6" t="n">
+      <c r="C72" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="E72" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="6" t="n">
         <v>1.5</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -7252,11 +7824,20 @@
       <c r="B73" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C73" s="6" t="n">
-        <v>1</v>
+      <c r="C73" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="D73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -7268,11 +7849,20 @@
       <c r="B74" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C74" s="6" t="n">
-        <v>1</v>
+      <c r="C74" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="D74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -7284,11 +7874,20 @@
       <c r="B75" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C75" s="6" t="n">
-        <v>1</v>
+      <c r="C75" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="D75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -7300,11 +7899,20 @@
       <c r="B76" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C76" s="6" t="n">
+      <c r="C76" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D76" s="6" t="n">
-        <v>1</v>
+      <c r="E76" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -7316,11 +7924,20 @@
       <c r="B77" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C77" s="6" t="n">
+      <c r="C77" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="E77" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="80" ht="29" customHeight="1">
@@ -7390,7 +8007,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B83" s="7" t="n">
+      <c r="B83" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C83" s="6" t="n">
@@ -7402,16 +8019,16 @@
       <c r="E83" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="F83" s="7" t="n">
+      <c r="F83" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H83" s="7" t="n">
+      <c r="H83" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I83" s="7" t="n">
+      <c r="I83" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7421,7 +8038,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B84" s="7" t="n">
+      <c r="B84" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C84" s="6" t="n">
@@ -7433,16 +8050,16 @@
       <c r="E84" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F84" s="7" t="n">
+      <c r="F84" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="G84" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H84" s="7" t="n">
+      <c r="H84" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I84" s="7" t="n">
+      <c r="I84" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7452,7 +8069,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B85" s="7" t="n">
+      <c r="B85" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C85" s="6" t="n">
@@ -7464,16 +8081,16 @@
       <c r="E85" s="6" t="n">
         <v>6.5</v>
       </c>
-      <c r="F85" s="7" t="n">
+      <c r="F85" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="G85" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H85" s="7" t="n">
+      <c r="H85" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I85" s="7" t="n">
+      <c r="I85" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7659,7 +8276,7 @@
           <t>Friedman</t>
         </is>
       </c>
-      <c r="C91" s="7" t="n">
+      <c r="C91" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D91" s="6" t="n">
@@ -7707,7 +8324,7 @@
       <c r="AD91" s="4" t="n"/>
       <c r="AE91" s="4" t="n"/>
     </row>
-    <row r="92" ht="35" customHeight="1">
+    <row r="92" ht="80" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Niederschlag_Uncertainty_Minima</t>
@@ -7718,7 +8335,7 @@
           <t>ANOVA (Messwiederholung)</t>
         </is>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C92" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D92" s="6" t="n">
@@ -7840,12 +8457,12 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
@@ -7933,15 +8550,20 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>Likert_Response</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>Gültig</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Zeit_s</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>IQR_auffällig</t>
         </is>
@@ -7981,13 +8603,16 @@
       <c r="I6" s="6" t="n">
         <v>41.02424631374638</v>
       </c>
-      <c r="J6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="6" t="n">
+      <c r="J6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6" t="n">
         <v>29.887</v>
       </c>
-      <c r="L6" s="4" t="b">
+      <c r="M6" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8025,13 +8650,16 @@
       <c r="I7" s="6" t="n">
         <v>68.81378549290919</v>
       </c>
-      <c r="J7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="6" t="n">
+      <c r="J7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6" t="n">
         <v>53.414</v>
       </c>
-      <c r="L7" s="4" t="b">
+      <c r="M7" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8069,13 +8697,16 @@
       <c r="I8" s="6" t="n">
         <v>99.82703565726457</v>
       </c>
-      <c r="J8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="6" t="n">
+      <c r="J8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6" t="n">
         <v>29.906</v>
       </c>
-      <c r="L8" s="4" t="b">
+      <c r="M8" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8113,13 +8744,16 @@
       <c r="I9" s="6" t="n">
         <v>54.64244904987003</v>
       </c>
-      <c r="J9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="6" t="n">
+      <c r="J9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="6" t="n">
         <v>61.133</v>
       </c>
-      <c r="L9" s="4" t="b">
+      <c r="M9" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8157,13 +8791,16 @@
       <c r="I10" s="6" t="n">
         <v>98.62117678364585</v>
       </c>
-      <c r="J10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="6" t="n">
+      <c r="J10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6" t="n">
         <v>25.372</v>
       </c>
-      <c r="L10" s="4" t="b">
+      <c r="M10" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8201,13 +8838,16 @@
       <c r="I11" s="6" t="n">
         <v>54.71660457690271</v>
       </c>
-      <c r="J11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="6" t="n">
+      <c r="J11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6" t="n">
         <v>14.751</v>
       </c>
-      <c r="L11" s="4" t="b">
+      <c r="M11" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8245,13 +8885,16 @@
       <c r="I12" s="6" t="n">
         <v>0.8348855774347732</v>
       </c>
-      <c r="J12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
+      <c r="J12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6" t="n">
         <v>101.057</v>
       </c>
-      <c r="L12" s="4" t="b">
+      <c r="M12" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8289,13 +8932,16 @@
       <c r="I13" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="6" t="n">
+      <c r="J13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="6" t="n">
         <v>50.307</v>
       </c>
-      <c r="L13" s="4" t="b">
+      <c r="M13" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8333,13 +8979,16 @@
       <c r="I14" s="6" t="n">
         <v>2.268689540744398</v>
       </c>
-      <c r="J14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="6" t="n">
+      <c r="J14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="6" t="n">
         <v>35.835</v>
       </c>
-      <c r="L14" s="4" t="b">
+      <c r="M14" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8377,13 +9026,16 @@
       <c r="I15" s="6" t="n">
         <v>39.48400275490717</v>
       </c>
-      <c r="J15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" s="6" t="n">
+      <c r="J15" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6" t="n">
         <v>44.672</v>
       </c>
-      <c r="L15" s="4" t="b">
+      <c r="M15" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8415,13 +9067,16 @@
       </c>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="n">
+      <c r="J16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6" t="n">
         <v>13.444</v>
       </c>
-      <c r="L16" s="4" t="b">
+      <c r="M16" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8459,13 +9114,16 @@
       <c r="I17" s="6" t="n">
         <v>15.57246501580943</v>
       </c>
-      <c r="J17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" s="6" t="n">
+      <c r="J17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="6" t="n">
         <v>21.607</v>
       </c>
-      <c r="L17" s="4" t="b">
+      <c r="M17" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8503,13 +9161,16 @@
       <c r="I18" s="6" t="n">
         <v>71.21082866355709</v>
       </c>
-      <c r="J18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="6" t="n">
+      <c r="J18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6" t="n">
         <v>106.218</v>
       </c>
-      <c r="L18" s="4" t="b">
+      <c r="M18" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8547,13 +9208,16 @@
       <c r="I19" s="6" t="n">
         <v>55.87433083930759</v>
       </c>
-      <c r="J19" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="6" t="n">
+      <c r="J19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6" t="n">
         <v>120.367</v>
       </c>
-      <c r="L19" s="4" t="b">
+      <c r="M19" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8591,13 +9255,16 @@
       <c r="I20" s="6" t="n">
         <v>50.5276977741601</v>
       </c>
-      <c r="J20" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" s="6" t="n">
+      <c r="J20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6" t="n">
         <v>125.329</v>
       </c>
-      <c r="L20" s="4" t="b">
+      <c r="M20" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8635,13 +9302,16 @@
       <c r="I21" s="6" t="n">
         <v>84.15380521554034</v>
       </c>
-      <c r="J21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="6" t="n">
+      <c r="J21" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="6" t="n">
         <v>131.408</v>
       </c>
-      <c r="L21" s="4" t="b">
+      <c r="M21" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8679,13 +9349,16 @@
       <c r="I22" s="6" t="n">
         <v>74.94541057508692</v>
       </c>
-      <c r="J22" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="6" t="n">
+      <c r="J22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="6" t="n">
         <v>277.851</v>
       </c>
-      <c r="L22" s="4" t="b">
+      <c r="M22" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8723,13 +9396,16 @@
       <c r="I23" s="6" t="n">
         <v>96.69489402999095</v>
       </c>
-      <c r="J23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="6" t="n">
+      <c r="J23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="6" t="n">
         <v>33.943</v>
       </c>
-      <c r="L23" s="4" t="b">
+      <c r="M23" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8767,13 +9443,16 @@
       <c r="I24" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J24" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="6" t="n">
+      <c r="J24" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="6" t="n">
         <v>29.395</v>
       </c>
-      <c r="L24" s="4" t="b">
+      <c r="M24" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8811,13 +9490,16 @@
       <c r="I25" s="6" t="n">
         <v>0.2361628525810126</v>
       </c>
-      <c r="J25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="6" t="n">
+      <c r="J25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6" t="n">
         <v>65.767</v>
       </c>
-      <c r="L25" s="4" t="b">
+      <c r="M25" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8855,13 +9537,16 @@
       <c r="I26" s="6" t="n">
         <v>0.2361628525810126</v>
       </c>
-      <c r="J26" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="6" t="n">
+      <c r="J26" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="6" t="n">
         <v>48.303</v>
       </c>
-      <c r="L26" s="4" t="b">
+      <c r="M26" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8899,13 +9584,16 @@
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" s="6" t="n">
+      <c r="J27" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="6" t="n">
         <v>25.174</v>
       </c>
-      <c r="L27" s="4" t="b">
+      <c r="M27" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8943,13 +9631,16 @@
       <c r="I28" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" s="6" t="n">
+      <c r="J28" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="6" t="n">
         <v>9.26</v>
       </c>
-      <c r="L28" s="4" t="b">
+      <c r="M28" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8987,13 +9678,16 @@
       <c r="I29" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" s="6" t="n">
+      <c r="J29" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="6" t="n">
         <v>9.605</v>
       </c>
-      <c r="L29" s="4" t="b">
+      <c r="M29" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9031,13 +9725,16 @@
       <c r="I30" s="6" t="n">
         <v>43.82552515418088</v>
       </c>
-      <c r="J30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" s="6" t="n">
+      <c r="J30" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="6" t="n">
         <v>25.319</v>
       </c>
-      <c r="L30" s="4" t="b">
+      <c r="M30" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9075,13 +9772,16 @@
       <c r="I31" s="6" t="n">
         <v>42.39622139435863</v>
       </c>
-      <c r="J31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" s="6" t="n">
+      <c r="J31" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6" t="n">
         <v>19.707</v>
       </c>
-      <c r="L31" s="4" t="b">
+      <c r="M31" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9119,13 +9819,16 @@
       <c r="I32" s="6" t="n">
         <v>43.11273205397098</v>
       </c>
-      <c r="J32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" s="6" t="n">
+      <c r="J32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" s="6" t="n">
         <v>14.743</v>
       </c>
-      <c r="L32" s="4" t="b">
+      <c r="M32" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9163,13 +9866,16 @@
       <c r="I33" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" s="6" t="n">
+      <c r="J33" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" s="6" t="n">
         <v>82.965</v>
       </c>
-      <c r="L33" s="4" t="b">
+      <c r="M33" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9207,13 +9913,16 @@
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" s="6" t="n">
+      <c r="J34" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="6" t="n">
         <v>39.092</v>
       </c>
-      <c r="L34" s="4" t="b">
+      <c r="M34" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9251,13 +9960,16 @@
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" s="6" t="n">
+      <c r="J35" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="6" t="n">
         <v>54.448</v>
       </c>
-      <c r="L35" s="4" t="b">
+      <c r="M35" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9295,13 +10007,16 @@
       <c r="I36" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" s="6" t="n">
+      <c r="J36" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="6" t="n">
         <v>8.978999999999999</v>
       </c>
-      <c r="L36" s="4" t="b">
+      <c r="M36" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9339,13 +10054,16 @@
       <c r="I37" s="6" t="n">
         <v>97.29244278871759</v>
       </c>
-      <c r="J37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K37" s="6" t="n">
+      <c r="J37" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="6" t="n">
         <v>91.72199999999999</v>
       </c>
-      <c r="L37" s="4" t="b">
+      <c r="M37" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9383,13 +10101,16 @@
       <c r="I38" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K38" s="6" t="n">
+      <c r="J38" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="6" t="n">
         <v>20.184</v>
       </c>
-      <c r="L38" s="4" t="b">
+      <c r="M38" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9427,13 +10148,16 @@
       <c r="I39" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" s="6" t="n">
+      <c r="J39" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="6" t="n">
         <v>33.024</v>
       </c>
-      <c r="L39" s="4" t="b">
+      <c r="M39" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9471,13 +10195,16 @@
       <c r="I40" s="6" t="n">
         <v>0.2361628525810126</v>
       </c>
-      <c r="J40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K40" s="6" t="n">
+      <c r="J40" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="6" t="n">
         <v>33.057</v>
       </c>
-      <c r="L40" s="4" t="b">
+      <c r="M40" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9515,13 +10242,16 @@
       <c r="I41" s="6" t="n">
         <v>0.3631468553360225</v>
       </c>
-      <c r="J41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K41" s="6" t="n">
+      <c r="J41" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" s="6" t="n">
         <v>16.51</v>
       </c>
-      <c r="L41" s="4" t="b">
+      <c r="M41" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9559,13 +10289,16 @@
       <c r="I42" s="6" t="n">
         <v>38.45365181729949</v>
       </c>
-      <c r="J42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K42" s="6" t="n">
+      <c r="J42" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" s="6" t="n">
         <v>125.092</v>
       </c>
-      <c r="L42" s="4" t="b">
+      <c r="M42" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9603,13 +10336,16 @@
       <c r="I43" s="6" t="n">
         <v>15.98080956704122</v>
       </c>
-      <c r="J43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K43" s="6" t="n">
+      <c r="J43" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" s="6" t="n">
         <v>75.002</v>
       </c>
-      <c r="L43" s="4" t="b">
+      <c r="M43" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9647,13 +10383,16 @@
       <c r="I44" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K44" s="6" t="n">
+      <c r="J44" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="6" t="n">
         <v>24.567</v>
       </c>
-      <c r="L44" s="4" t="b">
+      <c r="M44" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9691,13 +10430,16 @@
       <c r="I45" s="6" t="n">
         <v>0.176094919074602</v>
       </c>
-      <c r="J45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K45" s="6" t="n">
+      <c r="J45" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" s="6" t="n">
         <v>98.949</v>
       </c>
-      <c r="L45" s="4" t="b">
+      <c r="M45" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9735,13 +10477,16 @@
       <c r="I46" s="6" t="n">
         <v>0.2234448862035164</v>
       </c>
-      <c r="J46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K46" s="6" t="n">
+      <c r="J46" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" s="6" t="n">
         <v>109.417</v>
       </c>
-      <c r="L46" s="4" t="b">
+      <c r="M46" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9779,13 +10524,16 @@
       <c r="I47" s="6" t="n">
         <v>2.268689540744398</v>
       </c>
-      <c r="J47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K47" s="6" t="n">
+      <c r="J47" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" s="6" t="n">
         <v>42.354</v>
       </c>
-      <c r="L47" s="4" t="b">
+      <c r="M47" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9823,13 +10571,16 @@
       <c r="I48" s="6" t="n">
         <v>25.75603418589369</v>
       </c>
-      <c r="J48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K48" s="6" t="n">
+      <c r="J48" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" s="6" t="n">
         <v>19.371</v>
       </c>
-      <c r="L48" s="4" t="b">
+      <c r="M48" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9867,13 +10618,16 @@
       <c r="I49" s="6" t="n">
         <v>52.85704223147476</v>
       </c>
-      <c r="J49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K49" s="6" t="n">
+      <c r="J49" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" s="6" t="n">
         <v>32.175</v>
       </c>
-      <c r="L49" s="4" t="b">
+      <c r="M49" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9911,13 +10665,16 @@
       <c r="I50" s="6" t="n">
         <v>2.07146323138081</v>
       </c>
-      <c r="J50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K50" s="6" t="n">
+      <c r="J50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" s="6" t="n">
         <v>15.372</v>
       </c>
-      <c r="L50" s="4" t="b">
+      <c r="M50" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9931,7 +10688,7 @@
     <row r="54" ht="29" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Mittel = Summe / n; Median = mittlerer sortierter Wert; SD = Stichprobenstandardabweichung (ddof=1); Q1/Q3 = 25./75. Perzentil.</t>
+          <t>Mittel = Summe / n; Median = mittlerer sortierter Wert; SD = Stichprobenstandardabweichung (ddof=1); Q1/Q3 = 25./75. Perzentil; IQR = Q3 − Q1.</t>
         </is>
       </c>
     </row>
@@ -10003,10 +10760,15 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
+          <t>Fehler % IQR</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
           <t>Zeit s Mittel</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>Zeit s Median</t>
         </is>
@@ -10018,16 +10780,16 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B56" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="7" t="n">
+      <c r="C56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F56" s="6" t="n">
@@ -10055,9 +10817,12 @@
         <v>46.82021491406555</v>
       </c>
       <c r="N56" s="6" t="n">
+        <v>46.61408602823774</v>
+      </c>
+      <c r="O56" s="6" t="n">
         <v>33.83046666666667</v>
       </c>
-      <c r="O56" s="6" t="n">
+      <c r="P56" s="6" t="n">
         <v>24.567</v>
       </c>
     </row>
@@ -10067,16 +10832,16 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="C57" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="7" t="n">
+      <c r="C57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F57" s="6" t="n">
@@ -10104,9 +10869,12 @@
         <v>65.57892182950879</v>
       </c>
       <c r="N57" s="6" t="n">
+        <v>65.3522974517109</v>
+      </c>
+      <c r="O57" s="6" t="n">
         <v>71.60785714285713</v>
       </c>
-      <c r="O57" s="6" t="n">
+      <c r="P57" s="6" t="n">
         <v>51.8605</v>
       </c>
     </row>
@@ -10116,16 +10884,16 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B58" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="7" t="n">
+      <c r="C58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="8" t="n">
         <v>7</v>
       </c>
       <c r="F58" s="6" t="n">
@@ -10153,9 +10921,12 @@
         <v>42.42488573396363</v>
       </c>
       <c r="N58" s="6" t="n">
+        <v>42.24879081488903</v>
+      </c>
+      <c r="O58" s="6" t="n">
         <v>61.50953333333333</v>
       </c>
-      <c r="O58" s="6" t="n">
+      <c r="P58" s="6" t="n">
         <v>44.672</v>
       </c>
     </row>
@@ -10169,7 +10940,7 @@
     <row r="62" ht="29" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Nur vollständige Methodentripel; kleinster Fehler erhält Rang 1; Gleichstände erhalten Mittelränge.</t>
+          <t>Nur vollständige Methodentripel; kleinster Fehler erhält Rang 1; Gleichstände erhalten Mittelränge. Neben dem Rang steht die Likert-Sicherheit (1–7) je Methode.</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10957,27 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
+          <t>Likert_VSUP</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Likert_Scaled Glyph</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Likert_IsoGlyph</t>
         </is>
       </c>
     </row>
@@ -10204,11 +10990,20 @@
       <c r="B64" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C64" s="6" t="n">
+      <c r="C64" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D64" s="6" t="n">
-        <v>1</v>
+      <c r="E64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -10220,11 +11015,20 @@
       <c r="B65" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C65" s="6" t="n">
+      <c r="C65" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D65" s="6" t="n">
-        <v>1</v>
+      <c r="E65" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -10236,11 +11040,20 @@
       <c r="B66" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C66" s="6" t="n">
-        <v>1</v>
+      <c r="C66" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="D66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -10252,10 +11065,19 @@
       <c r="B67" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C67" s="6" t="n">
+      <c r="C67" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="E67" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" s="7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10268,11 +11090,20 @@
       <c r="B68" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="6" t="n">
-        <v>1</v>
+      <c r="C68" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="D68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -10284,11 +11115,20 @@
       <c r="B69" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="C69" s="6" t="n">
+      <c r="C69" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="D69" s="6" t="n">
-        <v>1</v>
+      <c r="E69" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -10300,11 +11140,20 @@
       <c r="B70" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="C70" s="6" t="n">
+      <c r="C70" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="D70" s="6" t="n">
-        <v>1</v>
+      <c r="E70" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -10316,11 +11165,20 @@
       <c r="B71" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="6" t="n">
-        <v>1</v>
+      <c r="C71" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="D71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -10332,11 +11190,20 @@
       <c r="B72" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="C72" s="6" t="n">
+      <c r="C72" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D72" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="E72" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -10348,11 +11215,20 @@
       <c r="B73" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="C73" s="6" t="n">
+      <c r="C73" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="E73" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" s="6" t="n">
         <v>1.5</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -10364,11 +11240,20 @@
       <c r="B74" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C74" s="6" t="n">
+      <c r="C74" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D74" s="6" t="n">
-        <v>1</v>
+      <c r="E74" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -10380,11 +11265,20 @@
       <c r="B75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="6" t="n">
+      <c r="C75" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="E75" s="7" t="n">
         <v>3</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -10396,11 +11290,20 @@
       <c r="B76" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C76" s="6" t="n">
+      <c r="C76" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D76" s="6" t="n">
-        <v>1</v>
+      <c r="E76" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -10412,11 +11315,20 @@
       <c r="B77" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C77" s="6" t="n">
+      <c r="C77" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="E77" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="80" ht="29" customHeight="1">
@@ -10486,7 +11398,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B83" s="7" t="n">
+      <c r="B83" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C83" s="6" t="n">
@@ -10498,16 +11410,16 @@
       <c r="E83" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F83" s="7" t="n">
+      <c r="F83" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H83" s="7" t="n">
+      <c r="H83" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I83" s="7" t="n">
+      <c r="I83" s="8" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10517,7 +11429,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B84" s="7" t="n">
+      <c r="B84" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C84" s="6" t="n">
@@ -10529,16 +11441,16 @@
       <c r="E84" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="F84" s="7" t="n">
+      <c r="F84" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="G84" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H84" s="7" t="n">
+      <c r="H84" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I84" s="7" t="n">
+      <c r="I84" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10548,7 +11460,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B85" s="7" t="n">
+      <c r="B85" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C85" s="6" t="n">
@@ -10560,16 +11472,16 @@
       <c r="E85" s="6" t="n">
         <v>6.5</v>
       </c>
-      <c r="F85" s="7" t="n">
+      <c r="F85" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="G85" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H85" s="7" t="n">
+      <c r="H85" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I85" s="7" t="n">
+      <c r="I85" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10755,7 +11667,7 @@
           <t>Friedman</t>
         </is>
       </c>
-      <c r="C91" s="7" t="n">
+      <c r="C91" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D91" s="6" t="n">
@@ -10803,7 +11715,7 @@
       <c r="AD91" s="4" t="n"/>
       <c r="AE91" s="4" t="n"/>
     </row>
-    <row r="92" ht="35" customHeight="1">
+    <row r="92" ht="80" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Luftdruck_Value_Maxima</t>
@@ -10814,7 +11726,7 @@
           <t>ANOVA (Messwiederholung)</t>
         </is>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C92" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D92" s="6" t="n">
@@ -10936,13 +11848,13 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
@@ -11029,15 +11941,20 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>Likert_Response</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>Gültig</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Zeit_s</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>IQR_auffällig</t>
         </is>
@@ -11077,13 +11994,16 @@
       <c r="I6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="J6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="6" t="n">
+      <c r="J6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6" t="n">
         <v>63.127</v>
       </c>
-      <c r="L6" s="4" t="b">
+      <c r="M6" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11121,13 +12041,16 @@
       <c r="I7" s="6" t="n">
         <v>25.05458942491307</v>
       </c>
-      <c r="J7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="6" t="n">
+      <c r="J7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6" t="n">
         <v>35.108</v>
       </c>
-      <c r="L7" s="4" t="b">
+      <c r="M7" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11165,13 +12088,16 @@
       <c r="I8" s="6" t="n">
         <v>37.37360298030865</v>
       </c>
-      <c r="J8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="6" t="n">
+      <c r="J8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6" t="n">
         <v>28.451</v>
       </c>
-      <c r="L8" s="4" t="b">
+      <c r="M8" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11209,13 +12135,16 @@
       <c r="I9" s="6" t="n">
         <v>84.65645837898778</v>
       </c>
-      <c r="J9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="6" t="n">
+      <c r="J9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="6" t="n">
         <v>10.491</v>
       </c>
-      <c r="L9" s="4" t="b">
+      <c r="M9" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11253,13 +12182,16 @@
       <c r="I10" s="6" t="n">
         <v>58.96557931315145</v>
       </c>
-      <c r="J10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="6" t="n">
+      <c r="J10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6" t="n">
         <v>22.625</v>
       </c>
-      <c r="L10" s="4" t="b">
+      <c r="M10" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11297,13 +12229,16 @@
       <c r="I11" s="6" t="n">
         <v>65.37230379112791</v>
       </c>
-      <c r="J11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="6" t="n">
+      <c r="J11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6" t="n">
         <v>23.941</v>
       </c>
-      <c r="L11" s="4" t="b">
+      <c r="M11" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11341,13 +12276,16 @@
       <c r="I12" s="6" t="n">
         <v>2.084963841843242</v>
       </c>
-      <c r="J12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
+      <c r="J12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6" t="n">
         <v>76.46599999999999</v>
       </c>
-      <c r="L12" s="4" t="b">
+      <c r="M12" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11385,13 +12323,16 @@
       <c r="I13" s="6" t="n">
         <v>3.126663118680212</v>
       </c>
-      <c r="J13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="6" t="n">
+      <c r="J13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="6" t="n">
         <v>41.663</v>
       </c>
-      <c r="L13" s="4" t="b">
+      <c r="M13" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11429,13 +12370,16 @@
       <c r="I14" s="6" t="n">
         <v>0.04128447547194585</v>
       </c>
-      <c r="J14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="6" t="n">
+      <c r="J14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="6" t="n">
         <v>106.515</v>
       </c>
-      <c r="L14" s="4" t="b">
+      <c r="M14" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11467,13 +12411,16 @@
       </c>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6" t="n">
+      <c r="J15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6" t="n">
         <v>44.919</v>
       </c>
-      <c r="L15" s="4" t="b">
+      <c r="M15" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11511,13 +12458,16 @@
       <c r="I16" s="6" t="n">
         <v>73.45075603418596</v>
       </c>
-      <c r="J16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" s="6" t="n">
+      <c r="J16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="6" t="n">
         <v>56.499</v>
       </c>
-      <c r="L16" s="4" t="b">
+      <c r="M16" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11549,13 +12499,16 @@
       </c>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6" t="n">
+      <c r="J17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6" t="n">
         <v>30.088</v>
       </c>
-      <c r="L17" s="4" t="b">
+      <c r="M17" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11593,13 +12546,16 @@
       <c r="I18" s="6" t="n">
         <v>16.7274520239176</v>
       </c>
-      <c r="J18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="6" t="n">
+      <c r="J18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6" t="n">
         <v>172.372</v>
       </c>
-      <c r="L18" s="4" t="b">
+      <c r="M18" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11637,13 +12593,16 @@
       <c r="I19" s="6" t="n">
         <v>53.82204238800372</v>
       </c>
-      <c r="J19" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="6" t="n">
+      <c r="J19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6" t="n">
         <v>146.478</v>
       </c>
-      <c r="L19" s="4" t="b">
+      <c r="M19" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11681,13 +12640,16 @@
       <c r="I20" s="6" t="n">
         <v>44.08986319381388</v>
       </c>
-      <c r="J20" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" s="6" t="n">
+      <c r="J20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6" t="n">
         <v>75.14400000000001</v>
       </c>
-      <c r="L20" s="4" t="b">
+      <c r="M20" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11725,13 +12687,16 @@
       <c r="I21" s="6" t="n">
         <v>1.636508781266623</v>
       </c>
-      <c r="J21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="6" t="n">
+      <c r="J21" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="6" t="n">
         <v>72.581</v>
       </c>
-      <c r="L21" s="4" t="b">
+      <c r="M21" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11769,13 +12734,16 @@
       <c r="I22" s="6" t="n">
         <v>59.25770121779424</v>
       </c>
-      <c r="J22" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="6" t="n">
+      <c r="J22" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="6" t="n">
         <v>44.285</v>
       </c>
-      <c r="L22" s="4" t="b">
+      <c r="M22" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11813,13 +12781,16 @@
       <c r="I23" s="6" t="n">
         <v>2.554745953729939</v>
       </c>
-      <c r="J23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="6" t="n">
+      <c r="J23" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="6" t="n">
         <v>49.409</v>
       </c>
-      <c r="L23" s="4" t="b">
+      <c r="M23" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11857,13 +12828,16 @@
       <c r="I24" s="6" t="n">
         <v>2.936284945058243</v>
       </c>
-      <c r="J24" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="6" t="n">
+      <c r="J24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="6" t="n">
         <v>25.678</v>
       </c>
-      <c r="L24" s="4" t="b">
+      <c r="M24" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11901,13 +12875,16 @@
       <c r="I25" s="6" t="n">
         <v>1.217402873869105</v>
       </c>
-      <c r="J25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="6" t="n">
+      <c r="J25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6" t="n">
         <v>14.895</v>
       </c>
-      <c r="L25" s="4" t="b">
+      <c r="M25" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11945,13 +12922,16 @@
       <c r="I26" s="6" t="n">
         <v>0.04128447547194585</v>
       </c>
-      <c r="J26" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="6" t="n">
+      <c r="J26" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="6" t="n">
         <v>45.795</v>
       </c>
-      <c r="L26" s="4" t="b">
+      <c r="M26" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11989,13 +12969,16 @@
       <c r="I27" s="6" t="n">
         <v>99.8239050809254</v>
       </c>
-      <c r="J27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" s="6" t="n">
+      <c r="J27" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="6" t="n">
         <v>9.292999999999999</v>
       </c>
-      <c r="L27" s="4" t="b">
+      <c r="M27" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12033,13 +13016,16 @@
       <c r="I28" s="6" t="n">
         <v>2.202360454559643</v>
       </c>
-      <c r="J28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" s="6" t="n">
+      <c r="J28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="6" t="n">
         <v>13.389</v>
       </c>
-      <c r="L28" s="4" t="b">
+      <c r="M28" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12077,13 +13063,16 @@
       <c r="I29" s="6" t="n">
         <v>94.07929749866966</v>
       </c>
-      <c r="J29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" s="6" t="n">
+      <c r="J29" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="6" t="n">
         <v>8.250999999999999</v>
       </c>
-      <c r="L29" s="4" t="b">
+      <c r="M29" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12121,13 +13110,16 @@
       <c r="I30" s="6" t="n">
         <v>83.40911936887602</v>
       </c>
-      <c r="J30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" s="6" t="n">
+      <c r="J30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="6" t="n">
         <v>29.765</v>
       </c>
-      <c r="L30" s="4" t="b">
+      <c r="M30" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12165,13 +13157,16 @@
       <c r="I31" s="6" t="n">
         <v>3.231341765018832</v>
       </c>
-      <c r="J31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" s="6" t="n">
+      <c r="J31" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6" t="n">
         <v>25.127</v>
       </c>
-      <c r="L31" s="4" t="b">
+      <c r="M31" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12209,13 +13204,16 @@
       <c r="I32" s="6" t="n">
         <v>59.39407694956648</v>
       </c>
-      <c r="J32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" s="6" t="n">
+      <c r="J32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" s="6" t="n">
         <v>88.18300000000001</v>
       </c>
-      <c r="L32" s="4" t="b">
+      <c r="M32" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12253,13 +13251,16 @@
       <c r="I33" s="6" t="n">
         <v>1.748818207431798</v>
       </c>
-      <c r="J33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" s="6" t="n">
+      <c r="J33" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" s="6" t="n">
         <v>49.395</v>
       </c>
-      <c r="L33" s="4" t="b">
+      <c r="M33" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12297,13 +13298,16 @@
       <c r="I34" s="6" t="n">
         <v>1.681119494098833</v>
       </c>
-      <c r="J34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" s="6" t="n">
+      <c r="J34" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="6" t="n">
         <v>55.436</v>
       </c>
-      <c r="L34" s="4" t="b">
+      <c r="M34" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12341,13 +13345,16 @@
       <c r="I35" s="6" t="n">
         <v>0.1729643427354296</v>
       </c>
-      <c r="J35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" s="6" t="n">
+      <c r="J35" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="6" t="n">
         <v>35.471</v>
       </c>
-      <c r="L35" s="4" t="b">
+      <c r="M35" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12385,13 +13392,16 @@
       <c r="I36" s="6" t="n">
         <v>2.084963841843242</v>
       </c>
-      <c r="J36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" s="6" t="n">
+      <c r="J36" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="6" t="n">
         <v>52.124</v>
       </c>
-      <c r="L36" s="4" t="b">
+      <c r="M36" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12429,13 +13439,16 @@
       <c r="I37" s="6" t="n">
         <v>2.520700936042364</v>
       </c>
-      <c r="J37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K37" s="6" t="n">
+      <c r="J37" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="6" t="n">
         <v>12.658</v>
       </c>
-      <c r="L37" s="4" t="b">
+      <c r="M37" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12473,13 +13486,16 @@
       <c r="I38" s="6" t="n">
         <v>3.562791534921518</v>
       </c>
-      <c r="J38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K38" s="6" t="n">
+      <c r="J38" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="6" t="n">
         <v>10.513</v>
       </c>
-      <c r="L38" s="4" t="b">
+      <c r="M38" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12517,13 +13533,16 @@
       <c r="I39" s="6" t="n">
         <v>0.04128447547194585</v>
       </c>
-      <c r="J39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" s="6" t="n">
+      <c r="J39" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="6" t="n">
         <v>26.138</v>
       </c>
-      <c r="L39" s="4" t="b">
+      <c r="M39" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12561,13 +13580,16 @@
       <c r="I40" s="6" t="n">
         <v>0.04128447547194585</v>
       </c>
-      <c r="J40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K40" s="6" t="n">
+      <c r="J40" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="6" t="n">
         <v>23.283</v>
       </c>
-      <c r="L40" s="4" t="b">
+      <c r="M40" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12605,13 +13627,16 @@
       <c r="I41" s="6" t="n">
         <v>1.67857590082322</v>
       </c>
-      <c r="J41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K41" s="6" t="n">
+      <c r="J41" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" s="6" t="n">
         <v>33.27</v>
       </c>
-      <c r="L41" s="4" t="b">
+      <c r="M41" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12649,13 +13674,16 @@
       <c r="I42" s="6" t="n">
         <v>57.02051310146209</v>
       </c>
-      <c r="J42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K42" s="6" t="n">
+      <c r="J42" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" s="6" t="n">
         <v>111.37</v>
       </c>
-      <c r="L42" s="4" t="b">
+      <c r="M42" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12693,13 +13721,16 @@
       <c r="I43" s="6" t="n">
         <v>43.15401652944321</v>
       </c>
-      <c r="J43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K43" s="6" t="n">
+      <c r="J43" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" s="6" t="n">
         <v>48.832</v>
       </c>
-      <c r="L43" s="4" t="b">
+      <c r="M43" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12737,13 +13768,16 @@
       <c r="I44" s="6" t="n">
         <v>99.8239050809254</v>
       </c>
-      <c r="J44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K44" s="6" t="n">
+      <c r="J44" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="6" t="n">
         <v>37.837</v>
       </c>
-      <c r="L44" s="4" t="b">
+      <c r="M44" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12781,13 +13815,16 @@
       <c r="I45" s="6" t="n">
         <v>55.59570954512723</v>
       </c>
-      <c r="J45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K45" s="6" t="n">
+      <c r="J45" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" s="6" t="n">
         <v>95.34699999999999</v>
       </c>
-      <c r="L45" s="4" t="b">
+      <c r="M45" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12825,13 +13862,16 @@
       <c r="I46" s="6" t="n">
         <v>1.750383495601384</v>
       </c>
-      <c r="J46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K46" s="6" t="n">
+      <c r="J46" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" s="6" t="n">
         <v>49.094</v>
       </c>
-      <c r="L46" s="4" t="b">
+      <c r="M46" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12869,13 +13909,16 @@
       <c r="I47" s="6" t="n">
         <v>99.29170710327777</v>
       </c>
-      <c r="J47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K47" s="6" t="n">
+      <c r="J47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" s="6" t="n">
         <v>142.791</v>
       </c>
-      <c r="L47" s="4" t="b">
+      <c r="M47" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12913,13 +13956,16 @@
       <c r="I48" s="6" t="n">
         <v>62.39825626897907</v>
       </c>
-      <c r="J48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K48" s="6" t="n">
+      <c r="J48" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" s="6" t="n">
         <v>15.442</v>
       </c>
-      <c r="L48" s="4" t="b">
+      <c r="M48" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12957,13 +14003,16 @@
       <c r="I49" s="6" t="n">
         <v>1.850561938452907</v>
       </c>
-      <c r="J49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K49" s="6" t="n">
+      <c r="J49" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" s="6" t="n">
         <v>17.722</v>
       </c>
-      <c r="L49" s="4" t="b">
+      <c r="M49" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13001,13 +14050,16 @@
       <c r="I50" s="6" t="n">
         <v>3.601728078139227</v>
       </c>
-      <c r="J50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K50" s="6" t="n">
+      <c r="J50" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" s="6" t="n">
         <v>15.017</v>
       </c>
-      <c r="L50" s="4" t="b">
+      <c r="M50" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13021,7 +14073,7 @@
     <row r="54" ht="29" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Mittel = Summe / n; Median = mittlerer sortierter Wert; SD = Stichprobenstandardabweichung (ddof=1); Q1/Q3 = 25./75. Perzentil.</t>
+          <t>Mittel = Summe / n; Median = mittlerer sortierter Wert; SD = Stichprobenstandardabweichung (ddof=1); Q1/Q3 = 25./75. Perzentil; IQR = Q3 − Q1.</t>
         </is>
       </c>
     </row>
@@ -13093,10 +14145,15 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
+          <t>Fehler % IQR</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
           <t>Zeit s Mittel</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>Zeit s Median</t>
         </is>
@@ -13108,16 +14165,16 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B56" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="C56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="7" t="n">
+      <c r="C56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
@@ -13145,9 +14202,12 @@
         <v>63.87774708073755</v>
       </c>
       <c r="N56" s="6" t="n">
+        <v>61.98012866668765</v>
+      </c>
+      <c r="O56" s="6" t="n">
         <v>50.04199999999999</v>
       </c>
-      <c r="O56" s="6" t="n">
+      <c r="P56" s="6" t="n">
         <v>36.654</v>
       </c>
     </row>
@@ -13157,16 +14217,16 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="7" t="n">
+      <c r="C57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
@@ -13194,9 +14254,12 @@
         <v>48.48802945872346</v>
       </c>
       <c r="N57" s="6" t="n">
+        <v>46.68755674169631</v>
+      </c>
+      <c r="O57" s="6" t="n">
         <v>40.47293333333334</v>
       </c>
-      <c r="O57" s="6" t="n">
+      <c r="P57" s="6" t="n">
         <v>35.108</v>
       </c>
     </row>
@@ -13206,16 +14269,16 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B58" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="C58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="7" t="n">
+      <c r="C58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
@@ -13243,9 +14306,12 @@
         <v>78.15640359390179</v>
       </c>
       <c r="N58" s="6" t="n">
+        <v>76.07143975205854</v>
+      </c>
+      <c r="O58" s="6" t="n">
         <v>57.82778571428572</v>
       </c>
-      <c r="O58" s="6" t="n">
+      <c r="P58" s="6" t="n">
         <v>50.7595</v>
       </c>
     </row>
@@ -13259,7 +14325,7 @@
     <row r="62" ht="29" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Nur vollständige Methodentripel; kleinster Fehler erhält Rang 1; Gleichstände erhalten Mittelränge.</t>
+          <t>Nur vollständige Methodentripel; kleinster Fehler erhält Rang 1; Gleichstände erhalten Mittelränge. Neben dem Rang steht die Likert-Sicherheit (1–7) je Methode.</t>
         </is>
       </c>
     </row>
@@ -13276,12 +14342,27 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
+          <t>Likert_VSUP</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Likert_Scaled Glyph</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Likert_IsoGlyph</t>
         </is>
       </c>
     </row>
@@ -13294,11 +14375,20 @@
       <c r="B64" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C64" s="6" t="n">
-        <v>1</v>
+      <c r="C64" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="D64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -13310,11 +14400,20 @@
       <c r="B65" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C65" s="6" t="n">
-        <v>1</v>
+      <c r="C65" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="D65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -13326,11 +14425,20 @@
       <c r="B66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C66" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="E66" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -13342,11 +14450,20 @@
       <c r="B67" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C67" s="6" t="n">
+      <c r="C67" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D67" s="6" t="n">
-        <v>1</v>
+      <c r="E67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -13358,11 +14475,20 @@
       <c r="B68" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C68" s="6" t="n">
+      <c r="C68" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D68" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D68" s="6" t="n">
-        <v>1</v>
+      <c r="E68" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -13374,11 +14500,20 @@
       <c r="B69" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C69" s="6" t="n">
+      <c r="C69" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="E69" s="7" t="n">
         <v>3</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -13390,11 +14525,20 @@
       <c r="B70" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C70" s="6" t="n">
-        <v>1</v>
+      <c r="C70" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="D70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="7" t="n">
         <v>3</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -13406,10 +14550,19 @@
       <c r="B71" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="6" t="n">
-        <v>1</v>
+      <c r="C71" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="D71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" s="7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13422,11 +14575,20 @@
       <c r="B72" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="6" t="n">
+      <c r="C72" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="E72" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -13438,11 +14600,20 @@
       <c r="B73" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C73" s="6" t="n">
+      <c r="C73" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D73" s="6" t="n">
-        <v>1</v>
+      <c r="E73" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -13454,12 +14625,21 @@
       <c r="B74" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C74" s="6" t="n">
-        <v>1.5</v>
+      <c r="C74" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="D74" s="6" t="n">
         <v>1.5</v>
       </c>
+      <c r="E74" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
@@ -13470,11 +14650,20 @@
       <c r="B75" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C75" s="6" t="n">
-        <v>1</v>
+      <c r="C75" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="D75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -13486,11 +14675,20 @@
       <c r="B76" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C76" s="6" t="n">
-        <v>1</v>
+      <c r="C76" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="D76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -13502,11 +14700,20 @@
       <c r="B77" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C77" s="6" t="n">
-        <v>1</v>
+      <c r="C77" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="D77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80" ht="29" customHeight="1">
@@ -13576,7 +14783,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B83" s="7" t="n">
+      <c r="B83" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C83" s="6" t="n">
@@ -13588,16 +14795,16 @@
       <c r="E83" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F83" s="7" t="n">
+      <c r="F83" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="H83" s="7" t="n">
+      <c r="H83" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I83" s="7" t="n">
+      <c r="I83" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13607,7 +14814,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B84" s="7" t="n">
+      <c r="B84" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C84" s="6" t="n">
@@ -13619,16 +14826,16 @@
       <c r="E84" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="F84" s="7" t="n">
+      <c r="F84" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="G84" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H84" s="7" t="n">
+      <c r="H84" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I84" s="7" t="n">
+      <c r="I84" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13638,7 +14845,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B85" s="7" t="n">
+      <c r="B85" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C85" s="6" t="n">
@@ -13650,16 +14857,16 @@
       <c r="E85" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="F85" s="7" t="n">
+      <c r="F85" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="G85" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H85" s="7" t="n">
+      <c r="H85" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I85" s="7" t="n">
+      <c r="I85" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13845,7 +15052,7 @@
           <t>Friedman</t>
         </is>
       </c>
-      <c r="C91" s="7" t="n">
+      <c r="C91" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D91" s="6" t="n">
@@ -13893,7 +15100,7 @@
       <c r="AD91" s="4" t="n"/>
       <c r="AE91" s="4" t="n"/>
     </row>
-    <row r="92" ht="35" customHeight="1">
+    <row r="92" ht="80" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Luftdruck_Value_Minima</t>
@@ -13904,7 +15111,7 @@
           <t>ANOVA (Messwiederholung)</t>
         </is>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C92" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D92" s="6" t="n">
@@ -14021,7 +15228,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
@@ -14377,7 +15584,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C25" s="6" t="n">
@@ -14405,7 +15612,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C26" s="6" t="n">
@@ -14433,7 +15640,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C27" s="6" t="n">
@@ -14465,7 +15672,7 @@
     <row r="31" ht="29" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Rang 1 = kleinster persönlicher Durchschnittsfehler.</t>
+          <t>Rang 1 = kleinster persönlicher Durchschnittsfehler; Likert_Mittel = mittlere vorhandene Sicherheitsbewertung über vier Aufgaben je Person/Methode.</t>
         </is>
       </c>
     </row>
@@ -14482,12 +15689,27 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
+          <t>Likert_Mittel_VSUP</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Likert_Mittel_Scaled Glyph</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Likert_Mittel_IsoGlyph</t>
         </is>
       </c>
     </row>
@@ -14501,10 +15723,19 @@
         <v>2</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1</v>
+        <v>2.75</v>
       </c>
       <c r="D33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F33" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -14517,10 +15748,19 @@
         <v>2</v>
       </c>
       <c r="C34" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="6" t="n">
-        <v>1</v>
+      <c r="E34" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -14533,10 +15773,19 @@
         <v>1</v>
       </c>
       <c r="C35" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D35" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="E35" s="6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F35" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -14549,10 +15798,19 @@
         <v>3</v>
       </c>
       <c r="C36" s="6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D36" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="6" t="n">
-        <v>1</v>
+      <c r="E36" s="6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -14565,10 +15823,19 @@
         <v>3</v>
       </c>
       <c r="C37" s="6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="6" t="n">
-        <v>1</v>
+      <c r="E37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -14581,10 +15848,19 @@
         <v>1</v>
       </c>
       <c r="C38" s="6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D38" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="E38" s="6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F38" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -14597,10 +15873,19 @@
         <v>2</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="D39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F39" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -14613,10 +15898,19 @@
         <v>2</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>1</v>
+        <v>4.75</v>
       </c>
       <c r="D40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -14629,10 +15923,19 @@
         <v>3</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F41" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -14645,10 +15948,19 @@
         <v>2</v>
       </c>
       <c r="C42" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D42" s="6" t="n">
-        <v>1</v>
+      <c r="E42" s="6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -14661,10 +15973,19 @@
         <v>3</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>1</v>
+        <v>4.75</v>
       </c>
       <c r="D43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F43" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -14677,10 +15998,19 @@
         <v>3</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="D44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F44" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -14693,10 +16023,19 @@
         <v>3</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1</v>
+        <v>4.75</v>
       </c>
       <c r="D45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F45" s="6" t="n">
         <v>2</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -14709,10 +16048,19 @@
         <v>1</v>
       </c>
       <c r="C46" s="6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D46" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="E46" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F46" s="6" t="n">
         <v>3</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49" ht="29" customHeight="1">
@@ -14782,7 +16130,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
+      <c r="B52" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C52" s="6" t="n">
@@ -14794,16 +16142,16 @@
       <c r="E52" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G52" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H52" s="7" t="n">
+      <c r="H52" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I52" s="7" t="n">
+      <c r="I52" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14813,7 +16161,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
+      <c r="B53" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C53" s="6" t="n">
@@ -14825,16 +16173,16 @@
       <c r="E53" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H53" s="7" t="n">
+      <c r="H53" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I53" s="7" t="n">
+      <c r="I53" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14844,7 +16192,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B54" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C54" s="6" t="n">
@@ -14856,16 +16204,16 @@
       <c r="E54" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F54" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G54" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H54" s="7" t="n">
+      <c r="H54" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I54" s="7" t="n">
+      <c r="I54" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15041,7 +16389,7 @@
           <t>Friedman</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D60" s="6" t="n">
@@ -15092,7 +16440,7 @@
           <t>ANOVA (Messwiederholung)</t>
         </is>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D61" s="6" t="n">
@@ -15311,7 +16659,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D6" s="6" t="n">
@@ -15357,7 +16705,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D7" s="6" t="n">
@@ -15403,7 +16751,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D8" s="6" t="n">
@@ -15449,7 +16797,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D9" s="6" t="n">
@@ -15495,7 +16843,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D10" s="6" t="n">
@@ -15541,7 +16889,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D11" s="6" t="n">
@@ -15643,7 +16991,7 @@
           <t>alle drei</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D17" s="6" t="n">
@@ -15675,7 +17023,7 @@
           <t>alle drei</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D18" s="6" t="n">
@@ -17525,7 +18873,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D6" s="6" t="n">
@@ -17543,7 +18891,7 @@
       <c r="H6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17558,7 +18906,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D7" s="6" t="n">
@@ -17576,7 +18924,7 @@
       <c r="H7" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17591,7 +18939,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D8" s="6" t="n">
@@ -17609,7 +18957,7 @@
       <c r="H8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17624,7 +18972,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D9" s="6" t="n">
@@ -17642,7 +18990,7 @@
       <c r="H9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17657,7 +19005,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D10" s="6" t="n">
@@ -17675,7 +19023,7 @@
       <c r="H10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17690,7 +19038,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D11" s="6" t="n">
@@ -17708,7 +19056,7 @@
       <c r="H11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17723,7 +19071,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D12" s="6" t="n">
@@ -17741,7 +19089,7 @@
       <c r="H12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17756,7 +19104,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D13" s="6" t="n">
@@ -17774,7 +19122,7 @@
       <c r="H13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17789,7 +19137,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D14" s="6" t="n">
@@ -17807,7 +19155,7 @@
       <c r="H14" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17822,7 +19170,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D15" s="6" t="n">
@@ -17840,7 +19188,7 @@
       <c r="H15" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17855,7 +19203,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D16" s="6" t="n">
@@ -17873,7 +19221,7 @@
       <c r="H16" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17888,7 +19236,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D17" s="6" t="n">
@@ -17906,7 +19254,7 @@
       <c r="H17" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -17978,7 +19326,7 @@
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="6" t="n">
@@ -17991,7 +19339,7 @@
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
@@ -18004,7 +19352,7 @@
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C8" s="6" t="n">
